--- a/artfynd/A 38688-2021 artfynd.xlsx
+++ b/artfynd/A 38688-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38688-2021 artfynd.xlsx
+++ b/artfynd/A 38688-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61080103</v>
+        <v>72117323</v>
       </c>
       <c r="B2" t="n">
-        <v>95710</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>15</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Köseven</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Agrostis clavata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Trin.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baggböle, Vb</t>
+          <t>Arboretrum Norr, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>751082.8297259625</v>
+        <v>751050</v>
       </c>
       <c r="R2" t="n">
-        <v>7089725.091506078</v>
+        <v>7089670</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-08-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-08-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-07-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,55 +758,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marcus Östman</t>
+          <t>Nils Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Östman, Elin Näsström</t>
+          <t>Nils Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72117323</v>
+        <v>72117338</v>
       </c>
       <c r="B3" t="n">
-        <v>97379</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>269</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Köseven</t>
+          <t>Älvstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Agrostis clavata</t>
+          <t>Carex rhynchophysa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Trin.</t>
+          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,13 +816,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751049.9742893165</v>
+        <v>751091</v>
       </c>
       <c r="R3" t="n">
-        <v>7089670.179272953</v>
+        <v>7089704</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,19 +849,9 @@
           <t>2018-07-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87313062</v>
+        <v>110580083</v>
       </c>
       <c r="B4" t="n">
-        <v>97379</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>269</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Köseven</t>
+          <t>Älvstarr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Agrostis clavata</t>
+          <t>Carex rhynchophysa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Trin.</t>
+          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arboretet norr (V Kåddisholmen), Vb</t>
+          <t>Norra arboretet, Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751105.9928574904</v>
+        <v>751093</v>
       </c>
       <c r="R4" t="n">
-        <v>7089629.929529733</v>
+        <v>7089676</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,111 +944,111 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-07-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-07-18</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hittade den ej trots mycket letande. En snarlik ven visade sig vara storven (hade underjordiska utlöpare mm).</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Älvstrand</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ulf Gärdenfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Patrik Engström</t>
+          <t>Ulf Gärdenfors, Sven Hellqvist, Åke Berg, Niklas Hjort</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100196126</v>
+        <v>98753907</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100399</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Turkos blåvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Aricia nicias</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Meigen, 1829)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baggböle, Umeå, Vb</t>
+          <t>Arboretum norr 6, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751093.1687688023</v>
+        <v>751119</v>
       </c>
       <c r="R5" t="n">
-        <v>7089673.645510948</v>
+        <v>7089676</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,22 +1072,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2020-07-08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämd via observation. Inventering utförd av: Philippe Simon (ej användare), Umu</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,33 +1101,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Magnusson</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Magnusson</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110580083</v>
+        <v>17012068</v>
       </c>
       <c r="B6" t="n">
-        <v>97069</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>17720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,34 +1131,58 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>269</v>
+        <v>101062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Älvstarr</t>
+          <t>Stubbträfluga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carex rhynchophysa</t>
+          <t>Hendelia beckeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Czerny, 1903</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norra arboretet, Baggböle, Vb</t>
+          <t>Baggböle: Arboretum Norr, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751092.9568095126</v>
+        <v>751114</v>
       </c>
       <c r="R6" t="n">
-        <v>7089676.286609831</v>
+        <v>7089675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,22 +1209,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:35</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,18 +1226,2114 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>lövdominerad, älvnära skog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Björk, bhd 347 mm., På stam, skuggad</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Sven Hellqvist</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors</t>
+          <t>Sven Hellqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulf Gärdenfors, Sven Hellqvist, Åke Berg, Niklas Hjort</t>
+          <t>Sven Hellqvist, Roger Mugerwa Pettersson, Marja Fors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>94180516</v>
+      </c>
+      <c r="B7" t="n">
+        <v>47010</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>101768</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Storfläckig kungsnattslända</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semblis phalaenoides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kåddisholmen, Umeälven, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>751002</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7089653</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-06-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Per-Anders Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>117772088</v>
+      </c>
+      <c r="B8" t="n">
+        <v>41714</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101978</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Springkornsfältmätare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Xanthorhoe biriviata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1794)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kåddis, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>750894</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7089823</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Andreas Press</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Andreas Press</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125203144</v>
+      </c>
+      <c r="B9" t="n">
+        <v>41714</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101978</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Springkornsfältmätare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Xanthorhoe biriviata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Borkhausen, 1794)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Arboretum Norr, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>751173</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7089637</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Jonsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonas Jonsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100705549</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Baggböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>751042</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7089746</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100503197</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57105</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Umeälven nedströms Kåddisholmen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>750968</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7089660</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maud Tyboni, Anne Jonsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>85787390</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57369</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102961</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Drillsnäppa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actitis hypoleucos</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Umeälven nedströms Kåddisholmen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>750968</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7089660</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-05-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100503222</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57546</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102963</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrattmås</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chroicocephalus ridibundus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Umeälven nedströms Kåddisholmen, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>750968</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7089660</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-05-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maud Tyboni, Anne Jonsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>98655221</v>
+      </c>
+      <c r="B14" t="n">
+        <v>29424</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103271</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tajgahumla</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bombus cingulatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Wahlberg, 1855</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>arbetare</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Arboretum norr 7, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>751165</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7089613</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Artbestämd via observation. Inventering utförd av: Philippe Simon (ej användare), Umu</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Natuschka Lee</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Natuschka Lee</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123940329</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Arboretum norr, Baggböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>751096</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7089706</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>död björk</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>98753920</v>
+      </c>
+      <c r="B16" t="n">
+        <v>43258</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>201129</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitfläckig guldvinge</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycaena virgaureae</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Arboretum norr 6, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>751119</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7089676</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-07-28</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Artbestämd via observation. Inventering utförd av: Cecilia Åström (ej användare), student Umu</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Natuschka Lee</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Natuschka Lee</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121182374</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56821</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>205988</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tajgafladdermus</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Myotis brandtii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Eversmann, 1845)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Arboretet, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>751110</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7089705</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>23:57</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121182391</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Arboretet, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>751110</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7089705</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-07-29</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121182309</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Arboretet, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>751110</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7089705</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marlene Olsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120507008</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Arboretum norr, Baggböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>751094</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7089719</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>61080103</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Baggböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>751083</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7089725</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2016-08-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2016-08-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marcus Östman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marcus Östman, Elin Näsström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123940324</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Arboretum norr, Baggböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>751063</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7089735</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100196126</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Baggböle, Umeå, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>751093</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7089674</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-04-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-04-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Magnusson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Magnusson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123940332</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Arboretum norr, Baggböle, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>751128</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7089676</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38688-2021 artfynd.xlsx
+++ b/artfynd/A 38688-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134947553</v>
+        <v>98753907</v>
       </c>
       <c r="B5" t="n">
-        <v>99961</v>
+        <v>43274</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +997,58 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>269</v>
+        <v>100399</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Älvstarr</t>
+          <t>Turkos blåvinge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex rhynchophysa</t>
+          <t>Aricia nicias</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fisch., C. A. Mey. &amp; Avé-Lall.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Meigen, 1829)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baggböle, Vb</t>
+          <t>Arboretum norr 6, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751109</v>
+        <v>751119</v>
       </c>
       <c r="R5" t="n">
-        <v>7089658</v>
+        <v>7089676</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,47 +1072,58 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ej noga undersökt. Kan vara blåsstarr.</t>
+          <t>Artbestämd via observation. Inventering utförd av: Philippe Simon (ej användare), Umu</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98753907</v>
+        <v>17012068</v>
       </c>
       <c r="B6" t="n">
-        <v>43274</v>
+        <v>17720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,21 +1131,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100399</v>
+        <v>101062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Turkos blåvinge</t>
+          <t>Stubbträfluga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Aricia nicias</t>
+          <t>Hendelia beckeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Meigen, 1829)</t>
+          <t>Czerny, 1903</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1131,23 +1163,26 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Arboretum norr 6, Vb</t>
+          <t>Baggböle: Arboretum Norr, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>751119</v>
+        <v>751114</v>
       </c>
       <c r="R6" t="n">
-        <v>7089676</v>
+        <v>7089675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,27 +1209,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Artbestämd via observation. Inventering utförd av: Philippe Simon (ej användare), Umu</t>
+          <t>2014-08-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,29 +1223,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>lövdominerad, älvnära skog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Björk, bhd 347 mm., På stam, skuggad</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Sven Hellqvist</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Natuschka Lee</t>
+          <t>Sven Hellqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Natuschka Lee</t>
+          <t>Sven Hellqvist, Roger Mugerwa Pettersson, Marja Fors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17012068</v>
+        <v>94180516</v>
       </c>
       <c r="B7" t="n">
-        <v>17720</v>
+        <v>47010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1233,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101062</v>
+        <v>101768</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbträfluga</t>
+          <t>Storfläckig kungsnattslända</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hendelia beckeri</t>
+          <t>Semblis phalaenoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Czerny, 1903</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1265,26 +1300,23 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Baggböle: Arboretum Norr, Vb</t>
+          <t>Kåddisholmen, Umeälven, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>751114</v>
+        <v>751002</v>
       </c>
       <c r="R7" t="n">
-        <v>7089675</v>
+        <v>7089653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,12 +1343,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-06-01</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-08-31</t>
+          <t>2021-06-10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,44 +1357,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>lövdominerad, älvnära skog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Björk, bhd 347 mm., På stam, skuggad</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Sven Hellqvist</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sven Hellqvist</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sven Hellqvist, Roger Mugerwa Pettersson, Marja Fors</t>
+          <t>Emil Larsson, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>94180516</v>
+        <v>117772088</v>
       </c>
       <c r="B8" t="n">
-        <v>47010</v>
+        <v>41714</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,21 +1387,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101768</v>
+        <v>101978</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Storfläckig kungsnattslända</t>
+          <t>Springkornsfältmätare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semblis phalaenoides</t>
+          <t>Xanthorhoe biriviata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Borkhausen, 1794)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1392,11 +1409,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -1411,17 +1424,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kåddisholmen, Umeälven, Vb</t>
+          <t>Kåddis, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>751002</v>
+        <v>750894</v>
       </c>
       <c r="R8" t="n">
-        <v>7089653</v>
+        <v>7089823</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,12 +1458,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-10</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,19 +1479,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil Larsson, Per-Anders Blomqvist</t>
+          <t>Andreas Press</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117772088</v>
+        <v>125203144</v>
       </c>
       <c r="B9" t="n">
         <v>41714</v>
@@ -1506,12 +1519,12 @@
           <t>(Borkhausen, 1794)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>imago/adult</t>
@@ -1523,20 +1536,24 @@
           <t>friflygande</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kåddis, Vb</t>
+          <t>Arboretum Norr, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750894</v>
+        <v>751173</v>
       </c>
       <c r="R9" t="n">
-        <v>7089823</v>
+        <v>7089637</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,12 +1577,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,88 +1601,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Jonas Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Press</t>
+          <t>Jonas Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125203144</v>
+        <v>134947556</v>
       </c>
       <c r="B10" t="n">
-        <v>41714</v>
+        <v>5175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101978</v>
+        <v>102185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Springkornsfältmätare</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Xanthorhoe biriviata</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Arboretum Norr, Umeå, Vb</t>
+          <t>Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>751173</v>
+        <v>751084</v>
       </c>
       <c r="R10" t="n">
-        <v>7089637</v>
+        <v>7089642</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,29 +1684,19 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>18:20</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1709,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonas Jonsson</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Jonsson</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134947556</v>
+        <v>100705549</v>
       </c>
       <c r="B11" t="n">
-        <v>5175</v>
+        <v>57132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1732,16 +1727,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102185</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1749,20 +1744,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>751084</v>
+        <v>751042</v>
       </c>
       <c r="R11" t="n">
-        <v>7089642</v>
+        <v>7089746</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,19 +1790,19 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1806,69 +1810,76 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Westman</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100705549</v>
+        <v>100503197</v>
       </c>
       <c r="B12" t="n">
-        <v>57132</v>
+        <v>57105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>102932</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Baggböle, Vb</t>
+          <t>Umeälven nedströms Kåddisholmen, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>751042</v>
+        <v>750968</v>
       </c>
       <c r="R12" t="n">
-        <v>7089746</v>
+        <v>7089660</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1892,12 +1903,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,22 +1923,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Maud Tyboni, Anne Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100503197</v>
+        <v>85787390</v>
       </c>
       <c r="B13" t="n">
-        <v>57105</v>
+        <v>57369</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,16 +1946,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102932</v>
+        <v>102961</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1954,15 +1965,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -2005,12 +2012,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2020-05-26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2030,17 +2037,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Maud Tyboni, Anne Jonsson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>85787390</v>
+        <v>100503222</v>
       </c>
       <c r="B14" t="n">
-        <v>57369</v>
+        <v>57546</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,26 +2055,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102961</v>
+        <v>102963</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Skrattmås</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Chroicocephalus ridibundus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2114,12 +2121,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-05-26</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,17 +2146,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Maud Tyboni, Anne Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100503222</v>
+        <v>98655221</v>
       </c>
       <c r="B15" t="n">
-        <v>57546</v>
+        <v>29424</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2157,49 +2164,66 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102963</v>
+        <v>103271</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrattmås</t>
+          <t>Tajgahumla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chroicocephalus ridibundus</t>
+          <t>Bombus cingulatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Wahlberg, 1855</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>arbetare</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Umeälven nedströms Kåddisholmen, Umeå, Vb</t>
+          <t>Arboretum norr 7, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750968</v>
+        <v>751165</v>
       </c>
       <c r="R15" t="n">
-        <v>7089660</v>
+        <v>7089613</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2223,12 +2247,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2020-07-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Artbestämd via observation. Inventering utförd av: Philippe Simon (ej användare), Umu</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,92 +2276,69 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Maud Tyboni, Anne Jonsson</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>98655221</v>
+        <v>123940329</v>
       </c>
       <c r="B16" t="n">
-        <v>29424</v>
+        <v>8444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103271</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgahumla</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bombus cingulatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Wahlberg, 1855</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>arbetare</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Arboretum norr 7, Vb</t>
+          <t>Arboretum norr, Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>751165</v>
+        <v>751096</v>
       </c>
       <c r="R16" t="n">
-        <v>7089613</v>
+        <v>7089706</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2349,27 +2365,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-07-08</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Artbestämd via observation. Inventering utförd av: Philippe Simon (ej användare), Umu</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,69 +2389,93 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>död björk</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Natuschka Lee</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Natuschka Lee</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123940329</v>
+        <v>98753920</v>
       </c>
       <c r="B17" t="n">
-        <v>8444</v>
+        <v>43258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106554</v>
+        <v>201129</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Arboretum norr, Baggböle, Vb</t>
+          <t>Arboretum norr 6, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>751096</v>
+        <v>751119</v>
       </c>
       <c r="R17" t="n">
-        <v>7089706</v>
+        <v>7089676</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,22 +2502,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2020-07-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Artbestämd via observation. Inventering utförd av: Cecilia Åström (ej användare), student Umu</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,96 +2531,76 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>död björk</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Natuschka Lee</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98753920</v>
+        <v>121182374</v>
       </c>
       <c r="B18" t="n">
-        <v>43258</v>
+        <v>56821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>201129</v>
+        <v>205988</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Tajgafladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Myotis brandtii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Eversmann, 1845)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Arboretum norr 6, Vb</t>
+          <t>Arboretet, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>751119</v>
+        <v>751110</v>
       </c>
       <c r="R18" t="n">
-        <v>7089676</v>
+        <v>7089705</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2604,27 +2624,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2020-07-28</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Artbestämd via observation. Inventering utförd av: Cecilia Åström (ej användare), student Umu</t>
+          <t>23:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,29 +2648,28 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Natuschka Lee</t>
+          <t>Marlene Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Natuschka Lee</t>
+          <t>Marlene Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121182374</v>
+        <v>121182391</v>
       </c>
       <c r="B19" t="n">
-        <v>56821</v>
+        <v>56823</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2663,21 +2677,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205988</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tajgafladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis brandtii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eversmann, 1845)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2726,22 +2740,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>23:57</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,36 +2782,44 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121182391</v>
+        <v>121182309</v>
       </c>
       <c r="B20" t="n">
-        <v>56823</v>
+        <v>56816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2842,22 +2864,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-07-29</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2884,32 +2906,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121182309</v>
+        <v>120507008</v>
       </c>
       <c r="B21" t="n">
-        <v>56816</v>
+        <v>58790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2917,32 +2939,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Arboretet, Umeå, Vb</t>
+          <t>Arboretum norr, Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>751110</v>
+        <v>751094</v>
       </c>
       <c r="R21" t="n">
-        <v>7089705</v>
+        <v>7089719</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2966,22 +2984,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>22:23</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>22:23</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,28 +2998,29 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marlene Olsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marlene Olsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120507008</v>
+        <v>61080103</v>
       </c>
       <c r="B22" t="n">
-        <v>58790</v>
+        <v>98186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3019,47 +3028,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208245</v>
+        <v>220250</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Arboretum norr, Baggböle, Vb</t>
+          <t>Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>751094</v>
+        <v>751083</v>
       </c>
       <c r="R22" t="n">
-        <v>7089719</v>
+        <v>7089725</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3086,12 +3085,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2016-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2016-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3100,26 +3099,25 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Marcus Östman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Marcus Östman, Elin Näsström</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>61080103</v>
+        <v>123940324</v>
       </c>
       <c r="B23" t="n">
         <v>98186</v>
@@ -3148,19 +3146,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Baggböle, Vb</t>
+          <t>Arboretum norr, Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>751083</v>
+        <v>751063</v>
       </c>
       <c r="R23" t="n">
-        <v>7089725</v>
+        <v>7089735</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3187,12 +3182,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2016-08-21</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2016-08-21</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3207,22 +3212,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marcus Östman</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marcus Östman, Elin Näsström</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123940324</v>
+        <v>100196126</v>
       </c>
       <c r="B24" t="n">
-        <v>98186</v>
+        <v>101326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3230,37 +3235,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220250</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Arboretum norr, Baggböle, Vb</t>
+          <t>Baggböle, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>751063</v>
+        <v>751093</v>
       </c>
       <c r="R24" t="n">
-        <v>7089735</v>
+        <v>7089674</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3284,22 +3295,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3314,19 +3315,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Magnus Magnusson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Magnus Magnusson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>100196126</v>
+        <v>123940332</v>
       </c>
       <c r="B25" t="n">
         <v>101326</v>
@@ -3355,25 +3356,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Baggböle, Umeå, Vb</t>
+          <t>Arboretum norr, Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>751093</v>
+        <v>751128</v>
       </c>
       <c r="R25" t="n">
-        <v>7089674</v>
+        <v>7089676</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3397,12 +3392,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3417,22 +3422,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Magnusson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Magnusson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123940332</v>
+        <v>135095349</v>
       </c>
       <c r="B26" t="n">
-        <v>101326</v>
+        <v>100806</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,37 +3445,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>222584</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Arboretum norr, Baggböle, Vb</t>
+          <t>Baggböle, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>751128</v>
+        <v>751111</v>
       </c>
       <c r="R26" t="n">
-        <v>7089676</v>
+        <v>7089687</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3494,22 +3499,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,112 +3519,15 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Bengt Westman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>135095349</v>
-      </c>
-      <c r="B27" t="n">
-        <v>100806</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>222584</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Bergsslok</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Melica nutans</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Baggböle, Vb</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>751111</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7089687</v>
-      </c>
-      <c r="S27" t="n">
-        <v>25</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Umeå</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Umeå socken</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Bengt Westman</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Bengt Westman</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
